--- a/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>fator</t>
   </si>
@@ -34,10 +34,16 @@
     <t>M (mortalidade natural)</t>
   </si>
   <si>
-    <t>M_Santos(2018)</t>
-  </si>
-  <si>
-    <t>Target_switch_M_Santos(2018)</t>
+    <t>M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_M_Santos(2005-2018)</t>
+  </si>
+  <si>
+    <t>M_Vieira(1988-2018)</t>
+  </si>
+  <si>
+    <t>Target_switch_M_Vieira(1988-2018)</t>
   </si>
   <si>
     <t>Bt/K (metodo de depleção)</t>
@@ -46,19 +52,19 @@
     <t>NN_CMSY</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1996-1999)</t>
+    <t>NN_CMSY_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Jardim(1996-1999)</t>
+    <t>zBRT_M_Jardim(1981-1994)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Jardim(1996-1999)</t>
+    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
   </si>
 </sst>
 </file>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -432,32 +438,32 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2094.255239626178</v>
+        <v>2097.498961788019</v>
       </c>
       <c r="E2">
-        <v>1.53496104384588</v>
+        <v>0.126588721225097</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
       <c r="D3">
-        <v>1808.012383372738</v>
+        <v>2120.447583356405</v>
       </c>
       <c r="E3">
-        <v>-12.34283986067042</v>
+        <v>1.222068259168723</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -466,15 +472,15 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2036.172144309533</v>
+        <v>1896.769409607813</v>
       </c>
       <c r="E4">
-        <v>-1.281059042289451</v>
+        <v>-9.455473382972697</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -483,10 +489,27 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>2139.454554982668</v>
+        <v>2081.936303982277</v>
       </c>
       <c r="E5">
-        <v>3.726341844568596</v>
+        <v>-0.6163131184956899</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>2201.94916344533</v>
+      </c>
+      <c r="E6">
+        <v>5.112642385001598</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
@@ -438,10 +438,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>2097.498961788019</v>
+        <v>1341.845049930966</v>
       </c>
       <c r="E2">
-        <v>0.126588721225097</v>
+        <v>0.3244915659434443</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -455,10 +455,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>2120.447583356405</v>
+        <v>1374.828057787021</v>
       </c>
       <c r="E3">
-        <v>1.222068259168723</v>
+        <v>2.79050170149863</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -472,10 +472,10 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1896.769409607813</v>
+        <v>1218.986938957394</v>
       </c>
       <c r="E4">
-        <v>-9.455473382972697</v>
+        <v>-8.861127532781806</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -489,10 +489,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>2081.936303982277</v>
+        <v>1230.762347646194</v>
       </c>
       <c r="E5">
-        <v>-0.6163131184956899</v>
+        <v>-7.980726409160367</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -506,10 +506,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>2201.94916344533</v>
+        <v>1403.802879020193</v>
       </c>
       <c r="E6">
-        <v>5.112642385001598</v>
+        <v>4.956835443670712</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
@@ -37,13 +37,13 @@
     <t>M_Santos(2005-2018)</t>
   </si>
   <si>
-    <t>Target_switch_M_Santos(2005-2018)</t>
+    <t>Target_switch_Santos (2018)</t>
   </si>
   <si>
     <t>M_Vieira(1988-2018)</t>
   </si>
   <si>
-    <t>Target_switch_M_Vieira(1988-2018)</t>
+    <t>Target_switch_Vieira (2019)</t>
   </si>
   <si>
     <t>Bt/K (metodo de depleção)</t>
@@ -52,19 +52,19 @@
     <t>NN_CMSY</t>
   </si>
   <si>
-    <t>NN_CMSY_M_Jardim(1981-1994)</t>
+    <t>NN_CMSY_Jardim (1999)</t>
   </si>
   <si>
     <t>zBRT</t>
   </si>
   <si>
-    <t>zBRT_M_Jardim(1981-1994)</t>
+    <t>zBRT_Jardim (1999)</t>
   </si>
   <si>
     <t>Uninformative_bk</t>
   </si>
   <si>
-    <t>Uninformative_bk_M_Jardim(1981-1994)</t>
+    <t>Uninformative_bk_Jardim (1999)</t>
   </si>
 </sst>
 </file>
@@ -438,10 +438,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1341.845049930966</v>
+        <v>1689.691650199756</v>
       </c>
       <c r="E2">
-        <v>0.3244915659434443</v>
+        <v>-0.821775760755271</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -455,10 +455,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1374.828057787021</v>
+        <v>1779.714733372287</v>
       </c>
       <c r="E3">
-        <v>2.79050170149863</v>
+        <v>4.462223558610451</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -472,10 +472,10 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1218.986938957394</v>
+        <v>1619.335823732185</v>
       </c>
       <c r="E4">
-        <v>-8.861127532781806</v>
+        <v>-4.951384812864412</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -489,10 +489,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1230.762347646194</v>
+        <v>1664.266437260831</v>
       </c>
       <c r="E5">
-        <v>-7.980726409160367</v>
+        <v>-2.314135310433515</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -506,10 +506,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1403.802879020193</v>
+        <v>1885.944024244911</v>
       </c>
       <c r="E6">
-        <v>4.956835443670712</v>
+        <v>10.6974632425466</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
@@ -438,10 +438,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1689.691650199756</v>
+        <v>1779.892877000475</v>
       </c>
       <c r="E2">
-        <v>-0.821775760755271</v>
+        <v>0.790995085046484</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -455,10 +455,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1779.714733372287</v>
+        <v>1809.239947653631</v>
       </c>
       <c r="E3">
-        <v>4.462223558610451</v>
+        <v>2.452848161815604</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -472,10 +472,10 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1619.335823732185</v>
+        <v>1708.684063534089</v>
       </c>
       <c r="E4">
-        <v>-4.951384812864412</v>
+        <v>-3.241386448047694</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -489,10 +489,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1664.266437260831</v>
+        <v>1733.742440530326</v>
       </c>
       <c r="E5">
-        <v>-2.314135310433515</v>
+        <v>-1.822391639257096</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -506,10 +506,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1885.944024244911</v>
+        <v>1918.338164500087</v>
       </c>
       <c r="E6">
-        <v>10.6974632425466</v>
+        <v>8.630814251825191</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
+++ b/Catch models/tornado_sensibilidade_msy_dbsra.xlsx
@@ -438,10 +438,10 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1779.892877000475</v>
+        <v>1794.76870347512</v>
       </c>
       <c r="E2">
-        <v>0.790995085046484</v>
+        <v>0.5876302730343698</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -455,10 +455,10 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>1809.239947653631</v>
+        <v>1823.742474777411</v>
       </c>
       <c r="E3">
-        <v>2.452848161815604</v>
+        <v>2.211462352191556</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -472,10 +472,10 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>1708.684063534089</v>
+        <v>1696.850683904675</v>
       </c>
       <c r="E4">
-        <v>-3.241386448047694</v>
+        <v>-4.900175219979246</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -489,10 +489,10 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>1733.742440530326</v>
+        <v>1747.040288031871</v>
       </c>
       <c r="E5">
-        <v>-1.822391639257096</v>
+        <v>-2.087303938169365</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -506,10 +506,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1918.338164500087</v>
+        <v>1937.033007604601</v>
       </c>
       <c r="E6">
-        <v>8.630814251825191</v>
+        <v>8.560818794273295</v>
       </c>
     </row>
   </sheetData>
